--- a/Output/PowerPoint_Figures/Fig_3/Fig_3c_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3c_data.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Surface 8</t>
+          <t>Cumulative Exposure</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -487,7 +487,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Surface 9</t>
+          <t>Recovery Model</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -513,7 +513,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Surface 3</t>
+          <t>Gaussian-Hill Hybrid</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Surface 2</t>
+          <t>Bivariate Gaussian</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -565,7 +565,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Surface 5</t>
+          <t>Gaussian Ridge</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Surface 6</t>
+          <t>Adaptive Response</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Surface 10</t>
+          <t>Modified Hill</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -643,7 +643,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Surface 12</t>
+          <t>Dual Hill Hormesis</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -669,7 +669,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Surface 7</t>
+          <t>Biphasic Response</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Surface 11</t>
+          <t>PKPD Elimination</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Surface 4</t>
+          <t>Hormesis Hill</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Surface 1</t>
+          <t>Dual Exponential</t>
         </is>
       </c>
       <c r="C13" t="n">

--- a/Output/PowerPoint_Figures/Fig_3/Fig_3c_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3c_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,34 +417,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Contractility</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>O2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,7 +460,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -482,7 +470,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -498,7 +486,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -508,7 +496,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -524,7 +512,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -534,7 +522,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -550,7 +538,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -560,7 +548,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,7 +564,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -586,7 +574,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -602,7 +590,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -612,7 +600,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -628,7 +616,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -638,7 +626,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -654,7 +642,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -664,7 +652,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -680,7 +668,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -690,7 +678,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -706,7 +694,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -716,7 +704,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -732,7 +720,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -742,7 +730,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -758,7 +746,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Excel_Figures\r2_equation_comparison.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Excel_Figures/r2_equation_comparison.xlsx</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">

--- a/Output/PowerPoint_Figures/Fig_3/Fig_3c_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3c_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R2_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="R2_Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Output/PowerPoint_Figures/Fig_3/Fig_3c_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3c_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="R2_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R2_Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
